--- a/SaidaRPA/Excel/tmr-distribuidora-indicador_01-02-2026_28-02-2026.xlsx
+++ b/SaidaRPA/Excel/tmr-distribuidora-indicador_01-02-2026_28-02-2026.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7108.89</v>
+        <v>6760.93</v>
       </c>
     </row>
     <row r="14">
